--- a/analysis/CBM/2025/Konte/data/results/IN1020_2025_CBM_konte_results_big_overview.xlsx
+++ b/analysis/CBM/2025/Konte/data/results/IN1020_2025_CBM_konte_results_big_overview.xlsx
@@ -452,735 +452,735 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>15262</v>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>54.25</v>
+        <v>29.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>15263</v>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="n">
-        <v>28.34</v>
+        <v>32.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>15264</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>27.62</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>15265</v>
       </c>
       <c r="B5" t="n">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="C5" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>15266</v>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>15268</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n">
-        <v>36.66</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>15270</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n">
-        <v>49.34999999999999</v>
+        <v>37.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>15272</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>15273</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D10" t="n">
-        <v>61.75</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>15274</v>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C11" t="n">
         <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>32.51</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>15275</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>20.7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>15276</v>
       </c>
       <c r="B13" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>31.74</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>15278</v>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="C14" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>68.5</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>15282</v>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>29.28</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>15283</v>
       </c>
       <c r="B16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>43.5</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15284</v>
       </c>
       <c r="B17" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C17" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" t="n">
-        <v>44.34999999999999</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15286</v>
       </c>
       <c r="B18" t="n">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>48.25</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>15288</v>
       </c>
       <c r="B19" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D19" t="n">
-        <v>61.91</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>15289</v>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C20" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D20" t="n">
-        <v>29.76</v>
+        <v>44.34999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>15290</v>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D21" t="n">
-        <v>48.75</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>15291</v>
       </c>
       <c r="B22" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C22" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>43.25</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>15292</v>
       </c>
       <c r="B23" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C23" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D23" t="n">
-        <v>48.75</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>15293</v>
       </c>
       <c r="B24" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D24" t="n">
-        <v>24.51</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>15294</v>
       </c>
       <c r="B25" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C25" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D25" t="n">
-        <v>60.5</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>15296</v>
       </c>
       <c r="B26" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C26" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>15297</v>
       </c>
       <c r="B27" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C27" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D27" t="n">
-        <v>41.24</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>15298</v>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C28" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D28" t="n">
-        <v>35.91</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>15299</v>
       </c>
       <c r="B29" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C29" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
-        <v>16.16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>15300</v>
       </c>
       <c r="B30" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C30" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
-        <v>35.25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>15301</v>
       </c>
       <c r="B31" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C31" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D31" t="n">
-        <v>37.91</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>15302</v>
       </c>
       <c r="B32" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C32" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D32" t="n">
-        <v>41.1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>15303</v>
       </c>
       <c r="B33" t="n">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="C33" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D33" t="n">
-        <v>15.91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>15304</v>
       </c>
       <c r="B34" t="n">
-        <v>62</v>
+        <v>-8</v>
       </c>
       <c r="C34" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>24.26</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>15305</v>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D35" t="n">
-        <v>51.16</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>15308</v>
       </c>
       <c r="B36" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C36" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>16.76</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>15309</v>
       </c>
       <c r="B37" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C37" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D37" t="n">
-        <v>39.66</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>15310</v>
       </c>
       <c r="B38" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C38" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D38" t="n">
-        <v>47.25</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>15311</v>
       </c>
       <c r="B39" t="n">
         <v>76</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D39" t="n">
-        <v>48.25</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>15312</v>
       </c>
       <c r="B40" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D40" t="n">
-        <v>50.75</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>15313</v>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C41" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D41" t="n">
-        <v>49</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>15314</v>
       </c>
       <c r="B42" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D42" t="n">
-        <v>51</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>15315</v>
       </c>
       <c r="B43" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C43" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D43" t="n">
-        <v>49.75</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>15316</v>
       </c>
       <c r="B44" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C44" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>15317</v>
       </c>
       <c r="B45" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C45" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D45" t="n">
-        <v>47.16</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>15318</v>
       </c>
       <c r="B46" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D46" t="n">
-        <v>39.57</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>15320</v>
       </c>
       <c r="B47" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C47" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D47" t="n">
-        <v>41.19</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>15321</v>
+      </c>
+      <c r="B48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
-        <v>86</v>
-      </c>
       <c r="C48" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D48" t="n">
-        <v>46.16</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>15322</v>
       </c>
       <c r="B49" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C49" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D49" t="n">
-        <v>42.5</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>15324</v>
       </c>
       <c r="B50" t="n">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="C50" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D50" t="n">
-        <v>60.5</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>15325</v>
       </c>
       <c r="B51" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C51" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D51" t="n">
-        <v>32.91</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>15326</v>
       </c>
       <c r="B52" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C52" t="n">
         <v>80</v>
       </c>
       <c r="D52" t="n">
-        <v>27.25</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>15327</v>
       </c>
       <c r="B53" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D53" t="n">
-        <v>47.75</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>15328</v>
       </c>
       <c r="B54" t="n">
         <v>52</v>
@@ -1194,212 +1194,212 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>15330</v>
       </c>
       <c r="B55" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C55" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D55" t="n">
-        <v>41.75</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>15331</v>
       </c>
       <c r="B56" t="n">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="C56" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D56" t="n">
-        <v>35.35</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>15333</v>
       </c>
       <c r="B57" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="C57" t="n">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D57" t="n">
-        <v>20.99</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>15334</v>
       </c>
       <c r="B58" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C58" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D58" t="n">
-        <v>35.2</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>15336</v>
       </c>
       <c r="B59" t="n">
-        <v>-8</v>
+        <v>103</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="D59" t="n">
-        <v>18.27</v>
+        <v>49.34999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>15337</v>
       </c>
       <c r="B60" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C60" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D60" t="n">
-        <v>30.1</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>15338</v>
       </c>
       <c r="B61" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C61" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D61" t="n">
-        <v>29</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>15342</v>
       </c>
       <c r="B62" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C62" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="D62" t="n">
-        <v>35.66</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>15343</v>
       </c>
       <c r="B63" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v>40.01</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>15344</v>
       </c>
       <c r="B64" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C64" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D64" t="n">
-        <v>52.75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>15348</v>
       </c>
       <c r="B65" t="n">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>24.82</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>15349</v>
       </c>
       <c r="B66" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C66" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D66" t="n">
-        <v>39.41</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>15351</v>
       </c>
       <c r="B67" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C67" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D67" t="n">
-        <v>62.75</v>
+        <v>56.31999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>15352</v>
       </c>
       <c r="B68" t="n">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="C68" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D68" t="n">
-        <v>37.5</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>15353</v>
       </c>
       <c r="B69" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C69" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D69" t="n">
-        <v>56.31999999999999</v>
+        <v>48.25</v>
       </c>
     </row>
   </sheetData>
